--- a/etf_holdings/2026-08-28_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:33</t>
+          <t>2026-08-28 06:33:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:33</t>
+          <t>2026-08-28 06:33:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:33</t>
+          <t>2026-08-28 06:33:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:33</t>
+          <t>2026-08-28 06:33:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:33</t>
+          <t>2026-08-28 06:33:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:33</t>
+          <t>2026-08-28 06:33:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:33</t>
+          <t>2026-08-28 06:33:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:33</t>
+          <t>2026-08-28 06:33:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:33</t>
+          <t>2026-08-28 06:33:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:33</t>
+          <t>2026-08-28 06:33:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:33</t>
+          <t>2026-08-28 06:33:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:33</t>
+          <t>2026-08-28 06:33:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:33</t>
+          <t>2026-08-28 06:33:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:33</t>
+          <t>2026-08-28 06:33:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:33</t>
+          <t>2026-08-28 06:33:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:35</t>
+          <t>2026-08-28 06:33:02</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:35</t>
+          <t>2026-08-28 06:33:02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:35</t>
+          <t>2026-08-28 06:33:02</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:35</t>
+          <t>2026-08-28 06:33:02</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:35</t>
+          <t>2026-08-28 06:33:02</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:35</t>
+          <t>2026-08-28 06:33:02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:35</t>
+          <t>2026-08-28 06:33:02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:35</t>
+          <t>2026-08-28 06:33:02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:35</t>
+          <t>2026-08-28 06:33:02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:35</t>
+          <t>2026-08-28 06:33:02</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:35</t>
+          <t>2026-08-28 06:33:02</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:35</t>
+          <t>2026-08-28 06:33:02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:35</t>
+          <t>2026-08-28 06:33:02</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:35</t>
+          <t>2026-08-28 06:33:02</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:35</t>
+          <t>2026-08-28 06:33:02</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:36</t>
+          <t>2026-08-28 06:33:03</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:36</t>
+          <t>2026-08-28 06:33:03</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:36</t>
+          <t>2026-08-28 06:33:03</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:36</t>
+          <t>2026-08-28 06:33:03</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:36</t>
+          <t>2026-08-28 06:33:03</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:36</t>
+          <t>2026-08-28 06:33:03</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:36</t>
+          <t>2026-08-28 06:33:03</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:36</t>
+          <t>2026-08-28 06:33:03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:36</t>
+          <t>2026-08-28 06:33:03</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:36</t>
+          <t>2026-08-28 06:33:03</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:36</t>
+          <t>2026-08-28 06:33:03</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:36</t>
+          <t>2026-08-28 06:33:03</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:36</t>
+          <t>2026-08-28 06:33:03</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:36</t>
+          <t>2026-08-28 06:33:03</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:36</t>
+          <t>2026-08-28 06:33:03</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:37</t>
+          <t>2026-08-28 06:33:04</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:37</t>
+          <t>2026-08-28 06:33:04</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:37</t>
+          <t>2026-08-28 06:33:04</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:37</t>
+          <t>2026-08-28 06:33:04</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:37</t>
+          <t>2026-08-28 06:33:04</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-28_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:00</t>
+          <t>2026-08-28 06:58:39</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:00</t>
+          <t>2026-08-28 06:58:39</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:00</t>
+          <t>2026-08-28 06:58:39</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:00</t>
+          <t>2026-08-28 06:58:39</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:00</t>
+          <t>2026-08-28 06:58:39</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:00</t>
+          <t>2026-08-28 06:58:39</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:00</t>
+          <t>2026-08-28 06:58:39</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:00</t>
+          <t>2026-08-28 06:58:39</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:00</t>
+          <t>2026-08-28 06:58:39</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:00</t>
+          <t>2026-08-28 06:58:39</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:00</t>
+          <t>2026-08-28 06:58:39</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:00</t>
+          <t>2026-08-28 06:58:39</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:00</t>
+          <t>2026-08-28 06:58:39</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:00</t>
+          <t>2026-08-28 06:58:39</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:00</t>
+          <t>2026-08-28 06:58:39</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:02</t>
+          <t>2026-08-28 06:58:41</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:02</t>
+          <t>2026-08-28 06:58:41</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:02</t>
+          <t>2026-08-28 06:58:41</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:02</t>
+          <t>2026-08-28 06:58:41</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:02</t>
+          <t>2026-08-28 06:58:41</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:02</t>
+          <t>2026-08-28 06:58:41</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:02</t>
+          <t>2026-08-28 06:58:41</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:02</t>
+          <t>2026-08-28 06:58:41</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:02</t>
+          <t>2026-08-28 06:58:41</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:02</t>
+          <t>2026-08-28 06:58:41</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:02</t>
+          <t>2026-08-28 06:58:41</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:02</t>
+          <t>2026-08-28 06:58:41</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:02</t>
+          <t>2026-08-28 06:58:41</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:02</t>
+          <t>2026-08-28 06:58:41</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:02</t>
+          <t>2026-08-28 06:58:41</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:03</t>
+          <t>2026-08-28 06:58:42</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:03</t>
+          <t>2026-08-28 06:58:42</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:03</t>
+          <t>2026-08-28 06:58:42</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:03</t>
+          <t>2026-08-28 06:58:42</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:03</t>
+          <t>2026-08-28 06:58:42</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:03</t>
+          <t>2026-08-28 06:58:42</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:03</t>
+          <t>2026-08-28 06:58:42</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:03</t>
+          <t>2026-08-28 06:58:42</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:03</t>
+          <t>2026-08-28 06:58:42</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:03</t>
+          <t>2026-08-28 06:58:42</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:03</t>
+          <t>2026-08-28 06:58:42</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:03</t>
+          <t>2026-08-28 06:58:42</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:03</t>
+          <t>2026-08-28 06:58:42</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:03</t>
+          <t>2026-08-28 06:58:42</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:03</t>
+          <t>2026-08-28 06:58:42</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:04</t>
+          <t>2026-08-28 06:58:43</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:04</t>
+          <t>2026-08-28 06:58:43</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:04</t>
+          <t>2026-08-28 06:58:43</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:04</t>
+          <t>2026-08-28 06:58:43</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:04</t>
+          <t>2026-08-28 06:58:43</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-28_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:39</t>
+          <t>2026-08-28 15:43:56</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,16 +509,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.21%2410</t>
+          <t>+0.41%2420</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>+0.41%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2410</v>
+        <v>2420</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:39</t>
+          <t>2026-08-28 15:43:56</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,16 +570,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+5.86%3340</t>
+          <t>+0.6%3360</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+5.86%</t>
+          <t>+0.6%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3340</v>
+        <v>3360</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.35%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:39</t>
+          <t>2026-08-28 15:43:56</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,16 +631,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+1.72%1180</t>
+          <t>-5.93%1110</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+1.72%</t>
+          <t>-5.93%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1180</v>
+        <v>1110</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.38%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:39</t>
+          <t>2026-08-28 15:43:56</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-6.7%5500</t>
+          <t>0%5490</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5500</v>
+        <v>5490</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:39</t>
+          <t>2026-08-28 15:43:56</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,16 +753,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-2.03%3865</t>
+          <t>+3.1%3985</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-2.03%</t>
+          <t>+3.1%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3865</v>
+        <v>3985</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:39</t>
+          <t>2026-08-28 15:43:56</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,16 +814,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-1.4%5645</t>
+          <t>+2.48%5785</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>+2.48%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>5645</v>
+        <v>5785</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:39</t>
+          <t>2026-08-28 15:43:56</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,16 +875,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-4.05%118.5</t>
+          <t>+9.7%130</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-4.05%</t>
+          <t>+9.7%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>118.5</v>
+        <v>130</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:39</t>
+          <t>2026-08-28 15:43:56</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,16 +936,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+0.99%5090</t>
+          <t>-1.18%5030</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5090</v>
+        <v>5030</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:39</t>
+          <t>2026-08-28 15:43:56</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,16 +997,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+3.35%555</t>
+          <t>+7.57%597</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+3.35%</t>
+          <t>+7.57%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>555</v>
+        <v>597</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:39</t>
+          <t>2026-08-28 15:43:56</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,16 +1058,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+1.14%1770</t>
+          <t>+3.39%1830</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+1.14%</t>
+          <t>+3.39%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1770</v>
+        <v>1830</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:39</t>
+          <t>2026-08-28 15:43:56</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,16 +1119,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+9.94%6915</t>
+          <t>+2.17%7065</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+9.94%</t>
+          <t>+2.17%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>6915</v>
+        <v>7065</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:39</t>
+          <t>2026-08-28 15:43:56</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,16 +1180,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+1.7%2090</t>
+          <t>+1.67%2125</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+1.7%</t>
+          <t>+1.67%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2090</v>
+        <v>2125</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:39</t>
+          <t>2026-08-28 15:43:56</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,16 +1241,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+0.44%6815</t>
+          <t>+5.65%7200</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>+5.65%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>6815</v>
+        <v>7200</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:39</t>
+          <t>2026-08-28 15:43:56</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,16 +1302,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+2.2%605</t>
+          <t>+2.64%621</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+2.2%</t>
+          <t>+2.64%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>605</v>
+        <v>621</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:39</t>
+          <t>2026-08-28 15:43:56</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,16 +1363,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+3.75%914</t>
+          <t>-1.64%899</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+3.75%</t>
+          <t>-1.64%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:41</t>
+          <t>2026-08-28 15:43:57</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,16 +1424,16 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-3.35%5920</t>
+          <t>+1.6%6015</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-3.35%</t>
+          <t>+1.6%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>5920</v>
+        <v>6015</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:41</t>
+          <t>2026-08-28 15:43:57</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,16 +1485,16 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+9.75%1295</t>
+          <t>-4.25%1240</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+9.75%</t>
+          <t>-4.25%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1295</v>
+        <v>1240</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:41</t>
+          <t>2026-08-28 15:43:57</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,16 +1546,16 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+2.48%186</t>
+          <t>-2.42%181.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+2.48%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>186</v>
+        <v>181.5</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:41</t>
+          <t>2026-08-28 15:43:57</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,16 +1607,16 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-5.56%1445</t>
+          <t>+3.11%1490</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-5.56%</t>
+          <t>+3.11%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1445</v>
+        <v>1490</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:41</t>
+          <t>2026-08-28 15:43:57</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,16 +1668,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-2.45%15305</t>
+          <t>+2.12%15630</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-2.45%</t>
+          <t>+2.12%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>15305</v>
+        <v>15630</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:41</t>
+          <t>2026-08-28 15:43:57</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,16 +1729,16 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+0.95%958</t>
+          <t>+1.46%972</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+0.95%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>958</v>
+        <v>972</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:41</t>
+          <t>2026-08-28 15:43:57</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,16 +1790,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+2.49%2055</t>
+          <t>+9.98%2260</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+2.49%</t>
+          <t>+9.98%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2055</v>
+        <v>2260</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:41</t>
+          <t>2026-08-28 15:43:57</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,16 +1851,16 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+9.9%227.5</t>
+          <t>-3.08%220.5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+9.9%</t>
+          <t>-3.08%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>227.5</v>
+        <v>220.5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:41</t>
+          <t>2026-08-28 15:43:57</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,16 +1912,16 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+9.62%1310</t>
+          <t>-3.44%1265</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+9.62%</t>
+          <t>-3.44%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1310</v>
+        <v>1265</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:41</t>
+          <t>2026-08-28 15:43:57</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,16 +1973,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+9.88%2225</t>
+          <t>+5.39%2345</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+9.88%</t>
+          <t>+5.39%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2225</v>
+        <v>2345</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:41</t>
+          <t>2026-08-28 15:43:57</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,16 +2034,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+0.51%1990</t>
+          <t>+1.01%2010</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+1.01%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1990</v>
+        <v>2010</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:41</t>
+          <t>2026-08-28 15:43:57</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,16 +2095,16 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-3.15%277</t>
+          <t>+3.61%287</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-3.15%</t>
+          <t>+3.61%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:41</t>
+          <t>2026-08-28 15:43:57</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,16 +2156,16 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+0.16%6345</t>
+          <t>+2.29%6490</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>+2.29%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>6345</v>
+        <v>6490</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:41</t>
+          <t>2026-08-28 15:43:57</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,16 +2217,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+2.23%252</t>
+          <t>+0.4%253</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+2.23%</t>
+          <t>+0.4%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:41</t>
+          <t>2026-08-28 15:43:57</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,16 +2278,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+9.2%397.5</t>
+          <t>+0.63%400</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+9.2%</t>
+          <t>+0.63%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>397.5</v>
+        <v>400</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:42</t>
+          <t>2026-08-28 15:43:59</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,16 +2339,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+2.56%760</t>
+          <t>-1.45%749</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+2.56%</t>
+          <t>-1.45%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>760</v>
+        <v>749</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:42</t>
+          <t>2026-08-28 15:43:59</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,16 +2400,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+1.59%127.5</t>
+          <t>-0.78%126.5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+1.59%</t>
+          <t>-0.78%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>127.5</v>
+        <v>126.5</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:42</t>
+          <t>2026-08-28 15:43:59</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,16 +2461,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0%14340</t>
+          <t>-0.28%14300</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>14340</v>
+        <v>14300</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:42</t>
+          <t>2026-08-28 15:43:59</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,16 +2522,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0%1625</t>
+          <t>+6.77%1735</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+6.77%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1625</v>
+        <v>1735</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:42</t>
+          <t>2026-08-28 15:43:59</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,16 +2583,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+9.9%494</t>
+          <t>+9.92%543</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+9.9%</t>
+          <t>+9.92%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>494</v>
+        <v>543</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:42</t>
+          <t>2026-08-28 15:43:59</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,16 +2644,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-0.93%1595</t>
+          <t>+1.25%1615</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-0.93%</t>
+          <t>+1.25%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1595</v>
+        <v>1615</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:42</t>
+          <t>2026-08-28 15:43:59</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-0.46%1075</t>
+          <t>0%1075</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-0.46%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:42</t>
+          <t>2026-08-28 15:43:59</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+0.7%578</t>
+          <t>+9.86%635</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+0.7%</t>
+          <t>+9.86%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>578</v>
+        <v>635</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:42</t>
+          <t>2026-08-28 15:43:59</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,16 +2827,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+1.17%690</t>
+          <t>+0.72%695</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+1.17%</t>
+          <t>+0.72%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:42</t>
+          <t>2026-08-28 15:43:59</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+5.42%75.8</t>
+          <t>+2.51%77.7</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+5.42%</t>
+          <t>+2.51%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>75.8</v>
+        <v>77.7</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:42</t>
+          <t>2026-08-28 15:43:59</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,16 +2949,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+0.92%219.5</t>
+          <t>+7.06%235</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+0.92%</t>
+          <t>+7.06%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>219.5</v>
+        <v>235</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:42</t>
+          <t>2026-08-28 15:43:59</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,16 +3010,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+2.43%590</t>
+          <t>-1.02%584</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+2.43%</t>
+          <t>-1.02%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:42</t>
+          <t>2026-08-28 15:43:59</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,16 +3071,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+1.24%245</t>
+          <t>+0.82%247</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+1.24%</t>
+          <t>+0.82%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:42</t>
+          <t>2026-08-28 15:43:59</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+1.17%433</t>
+          <t>+0.23%434</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+1.17%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:42</t>
+          <t>2026-08-28 15:43:59</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,16 +3193,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+1.41%2155</t>
+          <t>-0.23%2150</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+1.41%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>2155</v>
+        <v>2150</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:43</t>
+          <t>2026-08-28 15:44:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,16 +3254,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-0.5%497.5</t>
+          <t>-1.01%492.5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>-1.01%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>497.5</v>
+        <v>492.5</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:43</t>
+          <t>2026-08-28 15:44:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,16 +3315,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+5.3%477</t>
+          <t>+0.73%480.5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+5.3%</t>
+          <t>+0.73%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>477</v>
+        <v>480.5</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:43</t>
+          <t>2026-08-28 15:44:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,16 +3376,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+1.84%359.5</t>
+          <t>-1.53%354</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+1.84%</t>
+          <t>-1.53%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>359.5</v>
+        <v>354</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:43</t>
+          <t>2026-08-28 15:44:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,16 +3437,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-0.66%151</t>
+          <t>+1.32%153</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-0.66%</t>
+          <t>+1.32%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:43</t>
+          <t>2026-08-28 15:44:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-2.66%146.5</t>
+          <t>+5.12%154</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-2.66%</t>
+          <t>+5.12%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>146.5</v>
+        <v>154</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-08-28_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:56</t>
+          <t>2026-08-28 19:06:39</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,16 +522,16 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>17.19%12,000,000</t>
+          <t>16.02%11,100,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>17.19%</t>
+          <t>16.02%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>12000000</v>
+        <v>11100000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:56</t>
+          <t>2026-08-28 19:06:39</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -583,12 +583,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.25%3,150,000</t>
+          <t>6.31%3,150,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.25%</t>
+          <t>6.31%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:56</t>
+          <t>2026-08-28 19:06:39</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.93%8,460,000</t>
+          <t>5.60%8,460,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.93%</t>
+          <t>5.60%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>-0.36%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:56</t>
+          <t>2026-08-28 19:06:39</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -705,12 +705,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.23%1,600,000</t>
+          <t>5.24%1,600,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.23%</t>
+          <t>5.24%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:56</t>
+          <t>2026-08-28 19:06:39</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4.85%2,110,000</t>
+          <t>5.01%2,110,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4.85%</t>
+          <t>5.01%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:56</t>
+          <t>2026-08-28 19:06:39</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+2.48%5785</t>
+          <t>+9.7%130</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+2.48%</t>
+          <t>+9.7%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>5785</v>
+        <v>130</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.65%1,087,000</t>
+          <t>3.88%50,000,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.65%</t>
+          <t>3.88%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1087000</v>
+        <v>50000000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.35%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:56</t>
+          <t>2026-08-28 19:06:39</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+9.7%130</t>
+          <t>+2.48%5785</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+9.7%</t>
+          <t>+2.48%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>130</v>
+        <v>5785</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.52%50,000,000</t>
+          <t>3.75%1,087,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.52%</t>
+          <t>3.75%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>50000000</v>
+        <v>1087000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:56</t>
+          <t>2026-08-28 19:06:39</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>2327國巨*</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-1.18%5030</t>
+          <t>+7.57%597</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>+7.57%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5030</v>
+        <v>597</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.33%1,100,000</t>
+          <t>3.48%9,785,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.33%</t>
+          <t>3.48%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1100000</v>
+        <v>9785000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:56</t>
+          <t>2026-08-28 19:06:39</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2327國巨*</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+7.57%597</t>
+          <t>-1.18%5030</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+7.57%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>597</v>
+        <v>5030</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.23%9,785,000</t>
+          <t>3.30%1,100,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>3.30%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>9785000</v>
+        <v>1100000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:56</t>
+          <t>2026-08-28 19:06:39</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+3.39%1830</t>
+          <t>+2.17%7065</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+3.39%</t>
+          <t>+2.17%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1830</v>
+        <v>7065</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.03%2,880,000</t>
+          <t>3.20%760,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.03%</t>
+          <t>3.20%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>2880000</v>
+        <v>760000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:56</t>
+          <t>2026-08-28 19:06:39</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+2.17%7065</t>
+          <t>+3.39%1830</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+2.17%</t>
+          <t>+3.39%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>7065</v>
+        <v>1830</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.88%700,000</t>
+          <t>3.14%2,880,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.88%</t>
+          <t>3.14%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>700000</v>
+        <v>2880000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:56</t>
+          <t>2026-08-28 19:06:39</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+1.67%2125</t>
+          <t>+5.65%7200</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+1.67%</t>
+          <t>+5.65%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2125</v>
+        <v>7200</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.87%2,307,000</t>
+          <t>3.01%700,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.87%</t>
+          <t>3.01%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>2307000</v>
+        <v>700000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:56</t>
+          <t>2026-08-28 19:06:39</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+5.65%7200</t>
+          <t>+1.67%2125</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+5.65%</t>
+          <t>+1.67%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>7200</v>
+        <v>2125</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.67%660,000</t>
+          <t>2.92%2,307,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.67%</t>
+          <t>2.92%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>660000</v>
+        <v>2307000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:56</t>
+          <t>2026-08-28 19:06:39</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.52%7,000,000</t>
+          <t>2.59%7,000,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>2.59%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:56</t>
+          <t>2026-08-28 19:06:39</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.47%4,550,000</t>
+          <t>2.44%4,550,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>2.44%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:57</t>
+          <t>2026-08-28 19:06:40</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1437,20 +1437,20 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.19%621,000</t>
+          <t>2.33%650,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.19%</t>
+          <t>2.33%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>621000</v>
+        <v>650000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:57</t>
+          <t>2026-08-28 19:06:40</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.03%2,640,000</t>
+          <t>1.95%2,640,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>1.95%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:57</t>
+          <t>2026-08-28 19:06:40</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2344華邦電</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-2.42%181.5</t>
+          <t>+9.98%2260</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>+9.98%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>181.5</v>
+        <v>2260</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.66%15,000,000</t>
+          <t>1.74%1,293,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.74%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>15000000</v>
+        <v>1293000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:57</t>
+          <t>2026-08-28 19:06:40</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1620,12 +1620,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.63%1,900,000</t>
+          <t>1.69%1,900,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.69%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:57</t>
+          <t>2026-08-28 19:06:40</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>6488環球晶</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+2.12%15630</t>
+          <t>+1.46%972</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+2.12%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>15630</v>
+        <v>972</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.63%179,500</t>
+          <t>1.62%2,800,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.62%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>179500</v>
+        <v>2800000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:57</t>
+          <t>2026-08-28 19:06:40</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>6488環球晶</t>
+          <t>6805富世達</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+1.46%972</t>
+          <t>+5.39%2345</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>+5.39%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>972</v>
+        <v>2345</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.59%2,800,000</t>
+          <t>1.47%1,050,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.59%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>2800000</v>
+        <v>1050000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:57</t>
+          <t>2026-08-28 19:06:40</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>1303南亞</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+9.98%2260</t>
+          <t>-3.08%220.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+9.98%</t>
+          <t>-3.08%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2260</v>
+        <v>220.5</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.47%1,200,000</t>
+          <t>1.45%11,000,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.45%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>1200000</v>
+        <v>11000000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:57</t>
+          <t>2026-08-28 19:06:40</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1303南亞</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-3.08%220.5</t>
+          <t>+2.12%15630</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-3.08%</t>
+          <t>+2.12%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>220.5</v>
+        <v>15630</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.40%10,378,000</t>
+          <t>1.39%149,500</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.39%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>10378000</v>
+        <v>149500</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:57</t>
+          <t>2026-08-28 19:06:40</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.35%1,737,000</t>
+          <t>1.31%1,737,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>1.31%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:57</t>
+          <t>2026-08-28 19:06:40</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>6805富世達</t>
+          <t>2344華邦電</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+5.39%2345</t>
+          <t>-2.42%181.5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+5.39%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2345</v>
+        <v>181.5</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.24%936,000</t>
+          <t>1.30%12,000,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.30%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>936000</v>
+        <v>12000000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:57</t>
+          <t>2026-08-28 19:06:40</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.18%1,000,000</t>
+          <t>1.20%1,000,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.20%</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:57</t>
+          <t>2026-08-28 19:06:40</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.88%5,360,000</t>
+          <t>0.92%5,360,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.92%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:57</t>
+          <t>2026-08-28 19:06:40</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.49%130,000</t>
+          <t>0.50%130,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:57</t>
+          <t>2026-08-28 19:06:40</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,25 +2212,25 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2317鴻海</t>
+          <t>3211順達</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+0.4%253</t>
+          <t>+0.63%400</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+0.4%</t>
+          <t>+0.63%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>253</v>
+        <v>400</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.48%3,200,000</t>
+          <t>0.48%2,000,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>3200000</v>
+        <v>2000000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:57</t>
+          <t>2026-08-28 19:06:40</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,34 +2273,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3211順達</t>
+          <t>2317鴻海</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+0.63%400</t>
+          <t>+0.4%253</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+0.63%</t>
+          <t>+0.4%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>400</v>
+        <v>253</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.47%2,000,000</t>
+          <t>0.48%3,200,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>2000000</v>
+        <v>3200000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:59</t>
+          <t>2026-08-28 19:06:41</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:59</t>
+          <t>2026-08-28 19:06:41</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:59</t>
+          <t>2026-08-28 19:06:41</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:59</t>
+          <t>2026-08-28 19:06:41</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2535,12 +2535,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.24%250,000</t>
+          <t>0.26%250,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.24%</t>
+          <t>0.26%</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:59</t>
+          <t>2026-08-28 19:06:41</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>8358金居</t>
+          <t>6442光聖</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+9.92%543</t>
+          <t>+1.25%1615</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+9.92%</t>
+          <t>+1.25%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>543</v>
+        <v>1615</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.23%800,000</t>
+          <t>0.22%225,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.22%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>800000</v>
+        <v>225000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:59</t>
+          <t>2026-08-28 19:06:41</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,38 +2639,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>6442光聖</t>
+          <t>8358金居</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+1.25%1615</t>
+          <t>+9.92%543</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+1.25%</t>
+          <t>+9.92%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1615</v>
+        <v>543</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.21%225,000</t>
+          <t>0.19%600,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.19%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>225000</v>
+        <v>600000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:59</t>
+          <t>2026-08-28 19:06:41</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:59</t>
+          <t>2026-08-28 19:06:41</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2779,12 +2779,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.14%400,000</t>
+          <t>0.15%400,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>0.15%</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:59</t>
+          <t>2026-08-28 19:06:41</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,34 +2822,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1560中砂</t>
+          <t>1717長興</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+0.72%695</t>
+          <t>+2.51%77.7</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+0.72%</t>
+          <t>+2.51%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>695</v>
+        <v>77.7</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.12%300,000</t>
+          <t>0.13%2,800,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.13%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>300000</v>
+        <v>2800000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:59</t>
+          <t>2026-08-28 19:06:41</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,34 +2883,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1717長興</t>
+          <t>1560中砂</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+2.51%77.7</t>
+          <t>+0.72%695</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+2.51%</t>
+          <t>+0.72%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>77.7</v>
+        <v>695</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.11%2,500,000</t>
+          <t>0.12%300,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.12%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>2500000</v>
+        <v>300000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:59</t>
+          <t>2026-08-28 19:06:41</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.09%700,000</t>
+          <t>0.10%700,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>0.10%</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:59</t>
+          <t>2026-08-28 19:06:41</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:59</t>
+          <t>2026-08-28 19:06:41</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:59</t>
+          <t>2026-08-28 19:06:41</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-28 15:43:59</t>
+          <t>2026-08-28 19:06:41</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:00</t>
+          <t>2026-08-28 19:06:42</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:00</t>
+          <t>2026-08-28 19:06:42</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:00</t>
+          <t>2026-08-28 19:06:42</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:00</t>
+          <t>2026-08-28 19:06:42</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:00</t>
+          <t>2026-08-28 19:06:42</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-28_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:39</t>
+          <t>2026-08-28 20:38:21</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:39</t>
+          <t>2026-08-28 20:38:21</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:39</t>
+          <t>2026-08-28 20:38:21</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:39</t>
+          <t>2026-08-28 20:38:21</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:39</t>
+          <t>2026-08-28 20:38:21</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:39</t>
+          <t>2026-08-28 20:38:21</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:39</t>
+          <t>2026-08-28 20:38:21</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:39</t>
+          <t>2026-08-28 20:38:21</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:39</t>
+          <t>2026-08-28 20:38:21</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:39</t>
+          <t>2026-08-28 20:38:21</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:39</t>
+          <t>2026-08-28 20:38:21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:39</t>
+          <t>2026-08-28 20:38:21</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:39</t>
+          <t>2026-08-28 20:38:21</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:39</t>
+          <t>2026-08-28 20:38:21</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:39</t>
+          <t>2026-08-28 20:38:21</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:40</t>
+          <t>2026-08-28 20:38:22</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:40</t>
+          <t>2026-08-28 20:38:22</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:40</t>
+          <t>2026-08-28 20:38:22</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:40</t>
+          <t>2026-08-28 20:38:22</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:40</t>
+          <t>2026-08-28 20:38:22</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:40</t>
+          <t>2026-08-28 20:38:22</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:40</t>
+          <t>2026-08-28 20:38:22</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:40</t>
+          <t>2026-08-28 20:38:22</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:40</t>
+          <t>2026-08-28 20:38:22</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:40</t>
+          <t>2026-08-28 20:38:22</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:40</t>
+          <t>2026-08-28 20:38:22</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:40</t>
+          <t>2026-08-28 20:38:22</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:40</t>
+          <t>2026-08-28 20:38:22</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:40</t>
+          <t>2026-08-28 20:38:22</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:40</t>
+          <t>2026-08-28 20:38:22</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:41</t>
+          <t>2026-08-28 20:38:23</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:41</t>
+          <t>2026-08-28 20:38:23</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:41</t>
+          <t>2026-08-28 20:38:23</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:41</t>
+          <t>2026-08-28 20:38:23</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:41</t>
+          <t>2026-08-28 20:38:23</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:41</t>
+          <t>2026-08-28 20:38:23</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:41</t>
+          <t>2026-08-28 20:38:23</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:41</t>
+          <t>2026-08-28 20:38:23</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:41</t>
+          <t>2026-08-28 20:38:23</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:41</t>
+          <t>2026-08-28 20:38:23</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:41</t>
+          <t>2026-08-28 20:38:23</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:41</t>
+          <t>2026-08-28 20:38:23</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:41</t>
+          <t>2026-08-28 20:38:23</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:41</t>
+          <t>2026-08-28 20:38:23</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:41</t>
+          <t>2026-08-28 20:38:23</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:42</t>
+          <t>2026-08-28 20:38:24</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:42</t>
+          <t>2026-08-28 20:38:24</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:42</t>
+          <t>2026-08-28 20:38:24</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:42</t>
+          <t>2026-08-28 20:38:24</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-28 19:06:42</t>
+          <t>2026-08-28 20:38:24</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-28_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:21</t>
+          <t>2026-08-28 21:46:32</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:21</t>
+          <t>2026-08-28 21:46:32</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:21</t>
+          <t>2026-08-28 21:46:32</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:21</t>
+          <t>2026-08-28 21:46:32</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:21</t>
+          <t>2026-08-28 21:46:32</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:21</t>
+          <t>2026-08-28 21:46:32</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:21</t>
+          <t>2026-08-28 21:46:32</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:21</t>
+          <t>2026-08-28 21:46:32</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:21</t>
+          <t>2026-08-28 21:46:32</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:21</t>
+          <t>2026-08-28 21:46:32</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:21</t>
+          <t>2026-08-28 21:46:32</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:21</t>
+          <t>2026-08-28 21:46:32</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:21</t>
+          <t>2026-08-28 21:46:32</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:21</t>
+          <t>2026-08-28 21:46:32</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:21</t>
+          <t>2026-08-28 21:46:32</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:22</t>
+          <t>2026-08-28 21:46:33</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:22</t>
+          <t>2026-08-28 21:46:33</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:22</t>
+          <t>2026-08-28 21:46:33</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:22</t>
+          <t>2026-08-28 21:46:33</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:22</t>
+          <t>2026-08-28 21:46:33</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:22</t>
+          <t>2026-08-28 21:46:33</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:22</t>
+          <t>2026-08-28 21:46:33</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:22</t>
+          <t>2026-08-28 21:46:33</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:22</t>
+          <t>2026-08-28 21:46:33</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:22</t>
+          <t>2026-08-28 21:46:33</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:22</t>
+          <t>2026-08-28 21:46:33</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:22</t>
+          <t>2026-08-28 21:46:33</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:22</t>
+          <t>2026-08-28 21:46:33</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:22</t>
+          <t>2026-08-28 21:46:33</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:22</t>
+          <t>2026-08-28 21:46:33</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:23</t>
+          <t>2026-08-28 21:46:34</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:23</t>
+          <t>2026-08-28 21:46:34</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:23</t>
+          <t>2026-08-28 21:46:34</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:23</t>
+          <t>2026-08-28 21:46:34</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:23</t>
+          <t>2026-08-28 21:46:34</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:23</t>
+          <t>2026-08-28 21:46:34</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:23</t>
+          <t>2026-08-28 21:46:34</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:23</t>
+          <t>2026-08-28 21:46:34</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:23</t>
+          <t>2026-08-28 21:46:34</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:23</t>
+          <t>2026-08-28 21:46:34</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:23</t>
+          <t>2026-08-28 21:46:34</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:23</t>
+          <t>2026-08-28 21:46:34</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:23</t>
+          <t>2026-08-28 21:46:34</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:23</t>
+          <t>2026-08-28 21:46:34</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:23</t>
+          <t>2026-08-28 21:46:34</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:24</t>
+          <t>2026-08-28 21:46:36</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:24</t>
+          <t>2026-08-28 21:46:36</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:24</t>
+          <t>2026-08-28 21:46:36</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:24</t>
+          <t>2026-08-28 21:46:36</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:24</t>
+          <t>2026-08-28 21:46:36</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
